--- a/KURIKULUM2026_REVISI/032_MODALITAS_PEMBELAJARAN_KPT2024.xlsx
+++ b/KURIKULUM2026_REVISI/032_MODALITAS_PEMBELAJARAN_KPT2024.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>`STI-624` Integrasi AI, `STI-627` Platform Eng, `FST-610` Capstone</t>
+          <t>`STI-726` Integrasi AI, `STI-727` Platform Eng, `FST-610` Capstone</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>`STI-418` Dasar Keamanan Informasi, `STI-625` Smart City</t>
+          <t>`STI-418` Dasar Keamanan Informasi, `STI-727` Smart City</t>
         </is>
       </c>
     </row>
